--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,92 @@
         <v>24204</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980546</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.trigger.maple-retaliation</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>980544</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>980545</v>
+      </c>
+      <c r="I9" t="n">
+        <v>980551</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>980314</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980543</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.trigger.synwood-renewal-owner-turn</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>980541</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"type":"Turn","point":"Started"}</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>980542</v>
+      </c>
+      <c r="I10" t="n">
+        <v>980551</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>980313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,49 @@
         <v>980313</v>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1010543</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.trigger.weakness-break-reset</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1010541</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1010542</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1010551</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1010306</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,221 @@
         <v>1010306</v>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1020574</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.ordeal-freeze</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1020545</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1020555</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1020320</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1020570</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-wind-break</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1020541</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1020551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1020316</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1020571</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-lightning-break</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1020542</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1020552</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1020317</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1020572</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-imaginary-break</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020543</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1020553</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1020318</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1020573</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.formation-collapse</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1020544</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1020554</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1020565</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1020319</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,6 +1140,92 @@
         <v>1020319</v>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1030570</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.trigger.freeze-applied</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1030541</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"type":"Effect","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1030551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1030312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1030571</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.trigger.freeze-removed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1030542</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{"type":"Effect","point":"Removed"}</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1030552</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1030313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1226,49 @@
         <v>1030313</v>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1040571</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.trigger.tit-for-tat</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1040541</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1040551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1040561</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1040318</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,6 +1269,49 @@
         <v>1040318</v>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1050543</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.trigger.weakness-break-reset</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1050541</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1050542</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1050551</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1050305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,780 @@
         <v>1050305</v>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1060683</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-0-1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1060546</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1060646</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1060334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1060684</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-1-1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1060547</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1060647</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1060335</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1060685</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-2-1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1060548</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1060648</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1060336</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1060686</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-3-1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1060549</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1060649</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1060337</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1060673</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-break-1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1060542</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1060642</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1060330</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1060680</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-break-1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1060544</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1060644</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1060331</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1060671</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-actions-1</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1060541</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1060552</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1060325</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1060679</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-6</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1060553</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1060328</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1060681</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1060332</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1060687</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-weakness-last</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1060332</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060682</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-2</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1060333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060688</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-weakness-more</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1060333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060672</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-actions-2</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1060541</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1060557</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1060324</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1060678</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-5</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1060558</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1060327</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1060674</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1060570</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1060311</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1060675</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1060571</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1060312</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1060676</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1060572</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1060313</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1060677</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-4</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1060573</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1060314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2086,6 +2086,49 @@
         <v>1060314</v>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1070671</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.trigger.cruelty</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1070541</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1070641</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1070551</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1070309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2129,6 +2129,49 @@
         <v>1070309</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1095103</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.trigger.golden-hound-rebound</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1095101</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1095102</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1094801</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1091037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2172,6 +2172,49 @@
         <v>1091037</v>
       </c>
     </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1105103</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.trigger.automaton-spider-chains</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1105101</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1105102</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1104801</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1101040</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2215,6 +2215,49 @@
         <v>1101040</v>
       </c>
     </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1115103</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.trigger.illumination-dragonfish-candle-flame</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1115101</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1115102</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1114801</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1111031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2258,6 +2258,49 @@
         <v>1111031</v>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1125103</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.trigger.mara-struck-soldier-rebirth</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1125101</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1125102</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1124801</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1121038</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2301,6 +2301,49 @@
         <v>1121038</v>
       </c>
     </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1135103</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.trigger.silvermane-lieutenant-shield-reflect</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1135101</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1135102</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1134801</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1131060</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2344,6 +2344,49 @@
         <v>1131060</v>
       </c>
     </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1145103</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.trigger.voidranger-eliminator-detonated</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1145101</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1145102</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1144801</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1141041</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/RuleTrigger.xlsx
+++ b/config/data/RuleTrigger.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,1597 @@
         <v>24204</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980546</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.trigger.maple-retaliation</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>980544</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>980545</v>
+      </c>
+      <c r="I9" t="n">
+        <v>980551</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>980314</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980543</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.trigger.synwood-renewal-owner-turn</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>980541</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"type":"Turn","point":"Started"}</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>980542</v>
+      </c>
+      <c r="I10" t="n">
+        <v>980551</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>980313</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1010543</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.trigger.weakness-break-reset</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1010541</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1010542</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1010551</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1010306</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1020574</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.ordeal-freeze</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1020545</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1020555</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1020320</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1020570</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-wind-break</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1020541</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1020551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1020316</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1020571</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-lightning-break</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1020542</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1020552</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1020317</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1020572</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.core-imaginary-break</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1020543</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1020553</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1020561</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1020318</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1020573</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.trigger.formation-collapse</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1020544</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1020554</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1020565</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1020319</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1030570</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.trigger.freeze-applied</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1030541</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"type":"Effect","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1030551</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1030312</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1030571</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.trigger.freeze-removed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1030542</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{"type":"Effect","point":"Removed"}</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1030552</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1030561</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1030313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1040571</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.trigger.tit-for-tat</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1040541</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1040551</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1040561</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1040318</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1050543</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.trigger.weakness-break-reset</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1050541</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1050542</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1050551</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1050305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1060683</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-0-1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1060546</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1060646</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1060334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1060684</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-1-1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1060547</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1060647</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1060335</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1060685</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-2-1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1060548</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1060648</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1060336</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1060686</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-release-3-1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1060549</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1060649</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1060337</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1060673</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-break-1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1060542</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1060642</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1060330</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1060680</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-break-1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1060544</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1060644</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1060551</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1060331</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1060671</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-actions-1</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1060541</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1060552</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1060325</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1060679</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-6</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1060553</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1060328</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1060681</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1060332</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1060687</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-weakness-last</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1060554</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1060332</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060682</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-2</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1060333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060688</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.tomb-bars-weakness-more</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1060545</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{"type":"WeaknessBroken"}</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1060555</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1060333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060672</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.sunset-actions-2</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1060541</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1060557</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1060324</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1060678</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-5</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1060558</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1060327</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1060674</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1060570</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1060311</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1060675</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1060571</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1060312</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1060676</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1060572</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1060313</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1060677</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.trigger.nightfall-actions-4</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1060543</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>{"type":"Action","point":"Resolved"}</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1060573</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1060314</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1070671</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.trigger.cruelty</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1070541</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1070641</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1070551</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1070309</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1095103</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.trigger.golden-hound-rebound</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1095101</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1095102</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1094801</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1091037</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1105103</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.trigger.automaton-spider-chains</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1105101</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1105102</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1104801</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1101040</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1115103</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.trigger.illumination-dragonfish-candle-flame</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1115101</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1115102</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1114801</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1111031</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1125103</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.trigger.mara-struck-soldier-rebirth</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1125101</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>{"type":"Unit","point":"Defeated"}</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AfterDefeatSettlement</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1125102</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1124801</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1121038</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1135103</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.trigger.silvermane-lieutenant-shield-reflect</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1135101</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1135102</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1134801</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1131060</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1145103</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.trigger.voidranger-eliminator-detonated</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1145101</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>{"type":"Damage","point":"Applied"}</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AfterEvent</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1145102</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1144801</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1141041</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
